--- a/results/Directional_Rush_Analysis.xlsx
+++ b/results/Directional_Rush_Analysis.xlsx
@@ -1308,6 +1308,66 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C8:D10">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:F10">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:D7">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:F7">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D4">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:F4">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -1319,7 +1379,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F10">
+  <conditionalFormatting sqref="C11:D13">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1331,7 +1391,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:D7">
+  <conditionalFormatting sqref="E11:F13">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1343,7 +1403,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:F7">
+  <conditionalFormatting sqref="C14:D16">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1355,7 +1415,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D4">
+  <conditionalFormatting sqref="E14:F16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1367,7 +1427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:F4">
+  <conditionalFormatting sqref="C2:F4">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1379,7 +1439,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:D13">
+  <conditionalFormatting sqref="C5:F7">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1391,7 +1451,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:F13">
+  <conditionalFormatting sqref="C8:F10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1403,7 +1463,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D16">
+  <conditionalFormatting sqref="C11:F13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1415,7 +1475,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F16">
+  <conditionalFormatting sqref="C14:F16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
